--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.85725382767901</v>
+        <v>5.17680374699784</v>
       </c>
       <c r="D2" t="n">
-        <v>32.05551164166811</v>
+        <v>5.209020641771068</v>
       </c>
       <c r="E2" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F2" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.070565023211</v>
+        <v>12.36146681627179</v>
       </c>
       <c r="D3" t="n">
-        <v>20.25226705797784</v>
+        <v>3.290993396921398</v>
       </c>
       <c r="E3" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F3" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.08030653731164</v>
+        <v>3.263049812313141</v>
       </c>
       <c r="D4" t="n">
-        <v>19.91781386984566</v>
+        <v>3.23664475384992</v>
       </c>
       <c r="E4" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F4" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.06030102512382</v>
+        <v>11.05979891658262</v>
       </c>
       <c r="D5" t="n">
-        <v>31.605197272303</v>
+        <v>5.135844556749237</v>
       </c>
       <c r="E5" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F5" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>86.22325933233779</v>
+        <v>14.01127964150489</v>
       </c>
       <c r="D6" t="n">
-        <v>83.92988378037055</v>
+        <v>13.63860611431021</v>
       </c>
       <c r="E6" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F6" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>65.26630943702814</v>
+        <v>10.60577528351707</v>
       </c>
       <c r="D7" t="n">
-        <v>19.70477479141226</v>
+        <v>3.202025903604493</v>
       </c>
       <c r="E7" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F7" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>81.66694677986909</v>
+        <v>13.27087885172873</v>
       </c>
       <c r="D8" t="n">
-        <v>80.59418616893126</v>
+        <v>13.09655525245133</v>
       </c>
       <c r="E8" t="n">
-        <v>23.54788570958451</v>
+        <v>3.826531427807482</v>
       </c>
       <c r="F8" t="n">
-        <v>26.47692768476441</v>
+        <v>4.302500748774217</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
